--- a/experiments/results/resnet18/CIFAR-10/baseline/msp/adaptive/std/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/baseline/msp/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -715,6 +715,104 @@
       <c r="O7" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>97.48999999999999</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>86.98</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>38.01</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>30.11</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>95.39</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>94.58</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>94.67</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=0.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>90.08</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>25.07</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>96.22</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>26.32</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>95.76000000000001</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.0,type=std</t>
         </is>
       </c>
     </row>
